--- a/data/XRD/2 Round/Mo_400Sb_30Se.xlsx
+++ b/data/XRD/2 Round/Mo_400Sb_30Se.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fbdd27f2520478cf/Ambiente de Trabalho/TESE/Data_Analysis/data/XRD/2 Round/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{7FCEB614-DD27-46D2-A7E1-883C742C7B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1577A50B-5404-4FBD-91F1-6539A3486CD1}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{7FCEB614-DD27-46D2-A7E1-883C742C7B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF4A3CBB-898F-4B82-BF37-8AB6BEBC2BC4}"/>
   <bookViews>
-    <workbookView xWindow="3636" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{BD6B42E7-8F25-4A4F-8CC8-88E838C5844F}"/>
+    <workbookView xWindow="2880" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{BD6B42E7-8F25-4A4F-8CC8-88E838C5844F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="422">
   <si>
     <t>No.</t>
   </si>
@@ -119,9 +119,6 @@
     <t>Pure KA1</t>
   </si>
   <si>
-    <t>00-015-0861; 01-072-1184</t>
-  </si>
-  <si>
     <t>Search Peaks</t>
   </si>
   <si>
@@ -134,15 +131,6 @@
     <t>Profile fitting</t>
   </si>
   <si>
-    <t>96-900-8581</t>
-  </si>
-  <si>
-    <t>00-015-0861; 96-901-3009; 01-072-1184</t>
-  </si>
-  <si>
-    <t>00-015-0861; 01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>100,00</t>
   </si>
   <si>
@@ -161,21 +149,12 @@
     <t>13,41</t>
   </si>
   <si>
-    <t>00-015-0861; 96-900-8581; 01-072-1184</t>
-  </si>
-  <si>
     <t>10,48</t>
   </si>
   <si>
     <t>0,91</t>
   </si>
   <si>
-    <t>01-072-1184</t>
-  </si>
-  <si>
-    <t>01-085-0455; 01-072-1184</t>
-  </si>
-  <si>
     <t>0,11(1)</t>
   </si>
   <si>
@@ -278,9 +257,6 @@
     <t>781(30)</t>
   </si>
   <si>
-    <t>00-015-0861; 01-085-0568; 01-072-1184</t>
-  </si>
-  <si>
     <t>9,36</t>
   </si>
   <si>
@@ -521,9 +497,6 @@
     <t>561(23)</t>
   </si>
   <si>
-    <t>00-015-0861; 96-901-3125; 01-072-1184</t>
-  </si>
-  <si>
     <t>6,72</t>
   </si>
   <si>
@@ -548,9 +521,6 @@
     <t>8348(39)</t>
   </si>
   <si>
-    <t>96-901-3009</t>
-  </si>
-  <si>
     <t>0,480657</t>
   </si>
   <si>
@@ -683,9 +653,6 @@
     <t>67(9)</t>
   </si>
   <si>
-    <t>01-085-0455; 96-900-8581</t>
-  </si>
-  <si>
     <t>0,81</t>
   </si>
   <si>
@@ -728,9 +695,6 @@
     <t>141(14)</t>
   </si>
   <si>
-    <t>01-083-2437</t>
-  </si>
-  <si>
     <t>1,69</t>
   </si>
   <si>
@@ -827,9 +791,6 @@
     <t>316(13)</t>
   </si>
   <si>
-    <t>00-015-0861; 01-083-2437; 96-900-8581; 01-072-1184</t>
-  </si>
-  <si>
     <t>3,78</t>
   </si>
   <si>
@@ -899,9 +860,6 @@
     <t>126(11)</t>
   </si>
   <si>
-    <t>01-083-2437; 01-085-0568; 01-072-1184</t>
-  </si>
-  <si>
     <t>1,51</t>
   </si>
   <si>
@@ -926,9 +884,6 @@
     <t>76(16)</t>
   </si>
   <si>
-    <t>96-901-3125; 01-072-1184</t>
-  </si>
-  <si>
     <t>0,073248</t>
   </si>
   <si>
@@ -995,9 +950,6 @@
     <t>256(14)</t>
   </si>
   <si>
-    <t>01-085-0455</t>
-  </si>
-  <si>
     <t>3,07</t>
   </si>
   <si>
@@ -1019,9 +971,6 @@
     <t>51(9)</t>
   </si>
   <si>
-    <t>96-901-3129; 01-072-1184</t>
-  </si>
-  <si>
     <t>0,62</t>
   </si>
   <si>
@@ -1067,9 +1016,6 @@
     <t>202(12)</t>
   </si>
   <si>
-    <t>96-901-3125</t>
-  </si>
-  <si>
     <t>2,41</t>
   </si>
   <si>
@@ -1094,9 +1040,6 @@
     <t>34(10)</t>
   </si>
   <si>
-    <t>01-085-0568; 01-072-1184</t>
-  </si>
-  <si>
     <t>0,41</t>
   </si>
   <si>
@@ -1229,9 +1172,6 @@
     <t>121(20)</t>
   </si>
   <si>
-    <t>03-065-7442; 01-083-2437; 96-900-8581; 01-072-1184</t>
-  </si>
-  <si>
     <t>1,45</t>
   </si>
   <si>
@@ -1256,9 +1196,6 @@
     <t>284(11)</t>
   </si>
   <si>
-    <t>96-901-3012</t>
-  </si>
-  <si>
     <t>3,40</t>
   </si>
   <si>
@@ -1283,9 +1220,6 @@
     <t>145(10)</t>
   </si>
   <si>
-    <t>01-085-0455; 96-900-8581; 01-072-1184</t>
-  </si>
-  <si>
     <t>1,74</t>
   </si>
   <si>
@@ -1310,9 +1244,6 @@
     <t>204(11)</t>
   </si>
   <si>
-    <t>01-085-0455; 01-085-0568; 01-072-1184</t>
-  </si>
-  <si>
     <t>2,44</t>
   </si>
   <si>
@@ -1338,6 +1269,42 @@
   </si>
   <si>
     <t>0,197330</t>
+  </si>
+  <si>
+    <t>00-029-0914</t>
+  </si>
+  <si>
+    <t>34,3645</t>
+  </si>
+  <si>
+    <t>0,0129</t>
+  </si>
+  <si>
+    <t>2,52</t>
+  </si>
+  <si>
+    <t>1060,69</t>
+  </si>
+  <si>
+    <t>2,60754</t>
+  </si>
+  <si>
+    <t>146,31</t>
+  </si>
+  <si>
+    <t>00-015-0861; 00-029-0914</t>
+  </si>
+  <si>
+    <t>1,75</t>
+  </si>
+  <si>
+    <t>Manual input</t>
+  </si>
+  <si>
+    <t>0,017256</t>
+  </si>
+  <si>
+    <t>03-065-7442</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA4B8A9B-7994-4D7C-8BA3-BE0666BFC9CE}">
-  <dimension ref="A1:W49"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.3">
@@ -1792,10 +1759,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
         <v>23</v>
@@ -1807,37 +1774,37 @@
         <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M2" t="s">
         <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="O2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="P2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="R2" t="b">
         <v>1</v>
       </c>
       <c r="S2" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U2" t="s">
         <v>26</v>
       </c>
-      <c r="T2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U2" t="s">
-        <v>27</v>
-      </c>
       <c r="V2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
@@ -1845,10 +1812,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>23</v>
@@ -1860,40 +1827,40 @@
         <v>24</v>
       </c>
       <c r="L3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M3" t="s">
         <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O3" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="P3" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R3" t="b">
         <v>1</v>
       </c>
       <c r="S3" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="U3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
@@ -1901,10 +1868,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -1916,40 +1883,40 @@
         <v>24</v>
       </c>
       <c r="L4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="M4" t="s">
         <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="O4" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="P4" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R4" t="b">
         <v>1</v>
       </c>
       <c r="S4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T4" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="U4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
@@ -1957,10 +1924,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -1972,40 +1939,40 @@
         <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="M5" t="s">
         <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="O5" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="P5" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="Q5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R5" t="b">
         <v>1</v>
       </c>
       <c r="S5" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="T5" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="U5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.3">
@@ -2013,10 +1980,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -2028,40 +1995,40 @@
         <v>24</v>
       </c>
       <c r="L6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="M6" t="s">
         <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="O6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="P6" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="Q6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R6" t="b">
         <v>1</v>
       </c>
       <c r="S6" t="s">
-        <v>31</v>
+        <v>410</v>
       </c>
       <c r="T6" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="U6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W6" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.3">
@@ -2069,10 +2036,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -2084,40 +2051,40 @@
         <v>24</v>
       </c>
       <c r="L7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="M7" t="s">
         <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="P7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R7" t="b">
         <v>1</v>
       </c>
       <c r="S7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="U7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.3">
@@ -2125,10 +2092,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
         <v>23</v>
@@ -2140,40 +2107,40 @@
         <v>24</v>
       </c>
       <c r="L8" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="O8" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R8" t="b">
         <v>1</v>
       </c>
       <c r="S8" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T8" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="U8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W8" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.3">
@@ -2181,10 +2148,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
         <v>23</v>
@@ -2196,40 +2163,40 @@
         <v>24</v>
       </c>
       <c r="L9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
       </c>
       <c r="N9" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="O9" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="P9" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R9" t="b">
         <v>1</v>
       </c>
       <c r="S9" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="T9" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="U9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W9" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.3">
@@ -2237,10 +2204,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
         <v>23</v>
@@ -2252,40 +2219,40 @@
         <v>24</v>
       </c>
       <c r="L10" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
       </c>
       <c r="N10" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="O10" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="P10" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R10" t="b">
         <v>1</v>
       </c>
       <c r="S10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T10" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="U10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W10" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.3">
@@ -2293,10 +2260,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D11" t="s">
         <v>23</v>
@@ -2308,40 +2275,40 @@
         <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="M11" t="s">
         <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="O11" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="P11" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="Q11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R11" t="b">
         <v>1</v>
       </c>
       <c r="S11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T11" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="U11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W11" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.3">
@@ -2349,10 +2316,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>130</v>
+        <v>411</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>412</v>
       </c>
       <c r="D12" t="s">
         <v>23</v>
@@ -2364,40 +2331,37 @@
         <v>24</v>
       </c>
       <c r="L12" t="s">
-        <v>132</v>
+        <v>413</v>
       </c>
       <c r="M12" t="s">
         <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>133</v>
+        <v>414</v>
       </c>
       <c r="O12" t="s">
-        <v>134</v>
+        <v>415</v>
       </c>
       <c r="P12" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>29</v>
+        <v>416</v>
       </c>
       <c r="R12" t="b">
         <v>1</v>
       </c>
       <c r="S12" t="s">
-        <v>26</v>
+        <v>417</v>
       </c>
       <c r="T12" t="s">
-        <v>136</v>
+        <v>418</v>
       </c>
       <c r="U12" t="s">
-        <v>30</v>
+        <v>419</v>
       </c>
       <c r="V12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W12" t="s">
-        <v>137</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.3">
@@ -2405,10 +2369,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C13" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="D13" t="s">
         <v>23</v>
@@ -2420,40 +2384,40 @@
         <v>24</v>
       </c>
       <c r="L13" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="M13" t="s">
         <v>25</v>
       </c>
       <c r="N13" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="O13" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="P13" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="Q13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R13" t="b">
         <v>1</v>
       </c>
       <c r="S13" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T13" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="U13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W13" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.3">
@@ -2461,10 +2425,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="C14" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="D14" t="s">
         <v>23</v>
@@ -2476,40 +2440,40 @@
         <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="M14" t="s">
         <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="O14" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="P14" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R14" t="b">
         <v>1</v>
       </c>
       <c r="S14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T14" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="U14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W14" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.3">
@@ -2517,10 +2481,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="C15" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="D15" t="s">
         <v>23</v>
@@ -2532,40 +2496,40 @@
         <v>24</v>
       </c>
       <c r="L15" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="M15" t="s">
         <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="P15" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="Q15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R15" t="b">
         <v>1</v>
       </c>
       <c r="S15" t="s">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="T15" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="U15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W15" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.3">
@@ -2573,10 +2537,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="D16" t="s">
         <v>23</v>
@@ -2588,40 +2552,40 @@
         <v>24</v>
       </c>
       <c r="L16" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="M16" t="s">
         <v>25</v>
       </c>
       <c r="N16" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="O16" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="P16" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="Q16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R16" t="b">
         <v>1</v>
       </c>
       <c r="S16" t="s">
-        <v>169</v>
+        <v>31</v>
       </c>
       <c r="T16" t="s">
-        <v>34</v>
+        <v>152</v>
       </c>
       <c r="U16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W16" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:23" x14ac:dyDescent="0.3">
@@ -2629,10 +2593,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="C17" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
@@ -2644,40 +2608,37 @@
         <v>24</v>
       </c>
       <c r="L17" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="M17" t="s">
         <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="O17" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="P17" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R17" t="b">
-        <v>1</v>
-      </c>
-      <c r="S17" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T17" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="U17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W17" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:23" x14ac:dyDescent="0.3">
@@ -2685,10 +2646,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D18" t="s">
         <v>23</v>
@@ -2700,40 +2661,40 @@
         <v>24</v>
       </c>
       <c r="L18" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="M18" t="s">
         <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="O18" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="P18" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="Q18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R18" t="b">
         <v>1</v>
       </c>
       <c r="S18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T18" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="U18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W18" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.3">
@@ -2741,10 +2702,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="C19" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="D19" t="s">
         <v>23</v>
@@ -2756,40 +2717,40 @@
         <v>24</v>
       </c>
       <c r="L19" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="M19" t="s">
         <v>25</v>
       </c>
       <c r="N19" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="O19" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="P19" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="Q19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R19" t="b">
         <v>1</v>
       </c>
       <c r="S19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T19" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="U19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W19" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:23" x14ac:dyDescent="0.3">
@@ -2797,10 +2758,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="D20" t="s">
         <v>23</v>
@@ -2812,40 +2773,40 @@
         <v>24</v>
       </c>
       <c r="L20" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="M20" t="s">
         <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="O20" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="P20" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R20" t="b">
         <v>1</v>
       </c>
       <c r="S20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T20" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="U20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W20" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.3">
@@ -2853,10 +2814,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>186</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
@@ -2868,40 +2829,40 @@
         <v>24</v>
       </c>
       <c r="L21" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="M21" t="s">
         <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="O21" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="P21" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="Q21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R21" t="b">
         <v>1</v>
       </c>
       <c r="S21" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T21" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="U21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W21" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:23" x14ac:dyDescent="0.3">
@@ -2909,10 +2870,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="C22" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
         <v>23</v>
@@ -2924,40 +2885,40 @@
         <v>24</v>
       </c>
       <c r="L22" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
       <c r="M22" t="s">
         <v>25</v>
       </c>
       <c r="N22" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="O22" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="P22" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="Q22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R22" t="b">
         <v>1</v>
       </c>
       <c r="S22" t="s">
-        <v>214</v>
+        <v>31</v>
       </c>
       <c r="T22" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="U22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W22" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:23" x14ac:dyDescent="0.3">
@@ -2965,10 +2926,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
         <v>23</v>
@@ -2980,40 +2941,37 @@
         <v>24</v>
       </c>
       <c r="L23" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="M23" t="s">
         <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="O23" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="P23" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R23" t="b">
-        <v>1</v>
-      </c>
-      <c r="S23" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="U23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W23" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:23" x14ac:dyDescent="0.3">
@@ -3021,10 +2979,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="C24" t="s">
-        <v>224</v>
+        <v>34</v>
       </c>
       <c r="D24" t="s">
         <v>23</v>
@@ -3036,40 +2994,40 @@
         <v>24</v>
       </c>
       <c r="L24" t="s">
-        <v>225</v>
+        <v>35</v>
       </c>
       <c r="M24" t="s">
         <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="O24" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="P24" t="s">
-        <v>228</v>
+        <v>209</v>
       </c>
       <c r="Q24" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R24" t="b">
         <v>1</v>
       </c>
       <c r="S24" t="s">
-        <v>229</v>
+        <v>417</v>
       </c>
       <c r="T24" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="U24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W24" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:23" x14ac:dyDescent="0.3">
@@ -3077,10 +3035,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="D25" t="s">
         <v>23</v>
@@ -3092,40 +3050,37 @@
         <v>24</v>
       </c>
       <c r="L25" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="M25" t="s">
         <v>25</v>
       </c>
       <c r="N25" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="O25" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="P25" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R25" t="b">
-        <v>1</v>
-      </c>
-      <c r="S25" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T25" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="U25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W25" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:23" x14ac:dyDescent="0.3">
@@ -3133,10 +3088,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C26" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="D26" t="s">
         <v>23</v>
@@ -3148,40 +3103,40 @@
         <v>24</v>
       </c>
       <c r="L26" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="M26" t="s">
         <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="O26" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="P26" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="Q26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R26" t="b">
         <v>1</v>
       </c>
       <c r="S26" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="T26" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="U26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W26" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
     </row>
     <row r="27" spans="1:23" x14ac:dyDescent="0.3">
@@ -3189,10 +3144,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="C27" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="D27" t="s">
         <v>23</v>
@@ -3204,40 +3159,40 @@
         <v>24</v>
       </c>
       <c r="L27" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="M27" t="s">
         <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="O27" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="P27" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="Q27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R27" t="b">
         <v>1</v>
       </c>
       <c r="S27" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="T27" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="U27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W27" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:23" x14ac:dyDescent="0.3">
@@ -3245,10 +3200,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C28" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="D28" t="s">
         <v>23</v>
@@ -3260,40 +3215,40 @@
         <v>24</v>
       </c>
       <c r="L28" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="M28" t="s">
         <v>25</v>
       </c>
       <c r="N28" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="O28" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="P28" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="Q28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R28" t="b">
         <v>1</v>
       </c>
       <c r="S28" t="s">
-        <v>262</v>
+        <v>31</v>
       </c>
       <c r="T28" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="U28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W28" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
     </row>
     <row r="29" spans="1:23" x14ac:dyDescent="0.3">
@@ -3301,10 +3256,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D29" t="s">
         <v>23</v>
@@ -3316,40 +3271,40 @@
         <v>24</v>
       </c>
       <c r="L29" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="M29" t="s">
         <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="O29" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="P29" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="Q29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R29" t="b">
         <v>1</v>
       </c>
       <c r="S29" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="T29" t="s">
-        <v>41</v>
+        <v>250</v>
       </c>
       <c r="U29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W29" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:23" x14ac:dyDescent="0.3">
@@ -3357,10 +3312,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C30" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="D30" t="s">
         <v>23</v>
@@ -3372,40 +3327,40 @@
         <v>24</v>
       </c>
       <c r="L30" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="M30" t="s">
         <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="O30" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="P30" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="Q30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R30" t="b">
         <v>1</v>
       </c>
       <c r="S30" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T30" t="s">
-        <v>278</v>
+        <v>36</v>
       </c>
       <c r="U30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W30" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.3">
@@ -3413,10 +3368,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
         <v>23</v>
@@ -3428,40 +3383,40 @@
         <v>24</v>
       </c>
       <c r="L31" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="M31" t="s">
         <v>25</v>
       </c>
       <c r="N31" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
       <c r="O31" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
       <c r="P31" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="Q31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R31" t="b">
         <v>1</v>
       </c>
       <c r="S31" t="s">
-        <v>286</v>
+        <v>31</v>
       </c>
       <c r="T31" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="U31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W31" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.3">
@@ -3469,10 +3424,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="C32" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D32" t="s">
         <v>23</v>
@@ -3484,40 +3439,37 @@
         <v>24</v>
       </c>
       <c r="L32" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="M32" t="s">
         <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="O32" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="P32" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="Q32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R32" t="b">
-        <v>1</v>
-      </c>
-      <c r="S32" t="s">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>42</v>
+        <v>273</v>
       </c>
       <c r="U32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W32" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:23" x14ac:dyDescent="0.3">
@@ -3525,10 +3477,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="C33" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="D33" t="s">
         <v>23</v>
@@ -3540,40 +3492,37 @@
         <v>24</v>
       </c>
       <c r="L33" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="M33" t="s">
         <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="Q33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R33" t="b">
-        <v>1</v>
-      </c>
-      <c r="S33" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T33" t="s">
-        <v>303</v>
+        <v>37</v>
       </c>
       <c r="U33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W33" t="s">
-        <v>304</v>
+        <v>281</v>
       </c>
     </row>
     <row r="34" spans="1:23" x14ac:dyDescent="0.3">
@@ -3581,10 +3530,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>283</v>
       </c>
       <c r="D34" t="s">
         <v>23</v>
@@ -3596,40 +3545,37 @@
         <v>24</v>
       </c>
       <c r="L34" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s">
         <v>25</v>
       </c>
       <c r="N34" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="O34" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="P34" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="Q34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R34" t="b">
-        <v>1</v>
-      </c>
-      <c r="S34" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="U34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W34" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:23" x14ac:dyDescent="0.3">
@@ -3637,10 +3583,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="C35" t="s">
-        <v>313</v>
+        <v>32</v>
       </c>
       <c r="D35" t="s">
         <v>23</v>
@@ -3652,40 +3598,37 @@
         <v>24</v>
       </c>
       <c r="L35" t="s">
-        <v>314</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s">
         <v>25</v>
       </c>
       <c r="N35" t="s">
-        <v>315</v>
+        <v>292</v>
       </c>
       <c r="O35" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="P35" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="Q35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R35" t="b">
-        <v>1</v>
-      </c>
-      <c r="S35" t="s">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>319</v>
+        <v>295</v>
       </c>
       <c r="U35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W35" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.3">
@@ -3693,10 +3636,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="C36" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="D36" t="s">
         <v>23</v>
@@ -3708,40 +3651,40 @@
         <v>24</v>
       </c>
       <c r="L36" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s">
         <v>25</v>
       </c>
       <c r="N36" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="O36" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="P36" t="s">
-        <v>325</v>
+        <v>302</v>
       </c>
       <c r="Q36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R36" t="b">
         <v>1</v>
       </c>
       <c r="S36" t="s">
-        <v>326</v>
+        <v>410</v>
       </c>
       <c r="T36" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="U36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W36" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
     </row>
     <row r="37" spans="1:23" x14ac:dyDescent="0.3">
@@ -3749,10 +3692,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>329</v>
+        <v>305</v>
       </c>
       <c r="C37" t="s">
-        <v>330</v>
+        <v>276</v>
       </c>
       <c r="D37" t="s">
         <v>23</v>
@@ -3764,40 +3707,37 @@
         <v>24</v>
       </c>
       <c r="L37" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="M37" t="s">
         <v>25</v>
       </c>
       <c r="N37" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="O37" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="P37" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="Q37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R37" t="b">
-        <v>1</v>
-      </c>
-      <c r="S37" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="U37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W37" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
     </row>
     <row r="38" spans="1:23" x14ac:dyDescent="0.3">
@@ -3805,10 +3745,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>337</v>
+        <v>312</v>
       </c>
       <c r="C38" t="s">
-        <v>45</v>
+        <v>313</v>
       </c>
       <c r="D38" t="s">
         <v>23</v>
@@ -3820,40 +3760,37 @@
         <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>338</v>
+        <v>314</v>
       </c>
       <c r="M38" t="s">
         <v>25</v>
       </c>
       <c r="N38" t="s">
-        <v>339</v>
+        <v>315</v>
       </c>
       <c r="O38" t="s">
-        <v>340</v>
+        <v>316</v>
       </c>
       <c r="P38" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="Q38" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R38" t="b">
-        <v>1</v>
-      </c>
-      <c r="S38" t="s">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="U38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W38" t="s">
-        <v>344</v>
+        <v>319</v>
       </c>
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.3">
@@ -3861,10 +3798,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>345</v>
+        <v>320</v>
       </c>
       <c r="C39" t="s">
-        <v>346</v>
+        <v>38</v>
       </c>
       <c r="D39" t="s">
         <v>23</v>
@@ -3876,40 +3813,37 @@
         <v>24</v>
       </c>
       <c r="L39" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="M39" t="s">
         <v>25</v>
       </c>
       <c r="N39" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="O39" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="P39" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="Q39" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R39" t="b">
-        <v>1</v>
-      </c>
-      <c r="S39" t="s">
-        <v>351</v>
+        <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="U39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W39" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.3">
@@ -3917,10 +3851,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="C40" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="D40" t="s">
         <v>23</v>
@@ -3932,40 +3866,37 @@
         <v>24</v>
       </c>
       <c r="L40" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="M40" t="s">
         <v>25</v>
       </c>
       <c r="N40" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="O40" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="P40" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="Q40" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R40" t="b">
-        <v>1</v>
-      </c>
-      <c r="S40" t="s">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="U40" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W40" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.3">
@@ -3973,10 +3904,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="C41" t="s">
-        <v>38</v>
+        <v>336</v>
       </c>
       <c r="D41" t="s">
         <v>23</v>
@@ -3988,40 +3919,37 @@
         <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="M41" t="s">
         <v>25</v>
       </c>
       <c r="N41" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="O41" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="P41" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="Q41" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R41" t="b">
-        <v>1</v>
-      </c>
-      <c r="S41" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="U41" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W41" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.3">
@@ -4029,10 +3957,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="C42" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D42" t="s">
         <v>23</v>
@@ -4044,40 +3972,37 @@
         <v>24</v>
       </c>
       <c r="L42" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="M42" t="s">
         <v>25</v>
       </c>
       <c r="N42" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="O42" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="P42" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="Q42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R42" t="b">
-        <v>1</v>
-      </c>
-      <c r="S42" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
       <c r="U42" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W42" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.3">
@@ -4085,10 +4010,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C43" t="s">
-        <v>224</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
         <v>23</v>
@@ -4100,40 +4025,37 @@
         <v>24</v>
       </c>
       <c r="L43" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="M43" t="s">
         <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="O43" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="P43" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="Q43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R43" t="b">
-        <v>1</v>
-      </c>
-      <c r="S43" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>47</v>
+        <v>355</v>
       </c>
       <c r="U43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V43" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W43" t="s">
-        <v>381</v>
+        <v>356</v>
       </c>
     </row>
     <row r="44" spans="1:23" x14ac:dyDescent="0.3">
@@ -4141,10 +4063,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="C44" t="s">
-        <v>383</v>
+        <v>213</v>
       </c>
       <c r="D44" t="s">
         <v>23</v>
@@ -4156,40 +4078,37 @@
         <v>24</v>
       </c>
       <c r="L44" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="M44" t="s">
         <v>25</v>
       </c>
       <c r="N44" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="O44" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="P44" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="Q44" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R44" t="b">
-        <v>1</v>
-      </c>
-      <c r="S44" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>388</v>
+        <v>40</v>
       </c>
       <c r="U44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V44" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W44" t="s">
-        <v>389</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.3">
@@ -4197,10 +4116,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>390</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="D45" t="s">
         <v>23</v>
@@ -4212,40 +4131,37 @@
         <v>24</v>
       </c>
       <c r="L45" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="M45" t="s">
         <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>393</v>
+        <v>366</v>
       </c>
       <c r="O45" t="s">
-        <v>394</v>
+        <v>367</v>
       </c>
       <c r="P45" t="s">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="Q45" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R45" t="b">
-        <v>1</v>
-      </c>
-      <c r="S45" t="s">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="U45" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V45" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W45" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
     </row>
     <row r="46" spans="1:23" x14ac:dyDescent="0.3">
@@ -4253,10 +4169,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>399</v>
+        <v>371</v>
       </c>
       <c r="C46" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="D46" t="s">
         <v>23</v>
@@ -4268,40 +4184,40 @@
         <v>24</v>
       </c>
       <c r="L46" t="s">
-        <v>401</v>
+        <v>373</v>
       </c>
       <c r="M46" t="s">
         <v>25</v>
       </c>
       <c r="N46" t="s">
-        <v>402</v>
+        <v>374</v>
       </c>
       <c r="O46" t="s">
-        <v>403</v>
+        <v>375</v>
       </c>
       <c r="P46" t="s">
-        <v>404</v>
+        <v>376</v>
       </c>
       <c r="Q46" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R46" t="b">
         <v>1</v>
       </c>
       <c r="S46" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="T46" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="U46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W46" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
     </row>
     <row r="47" spans="1:23" x14ac:dyDescent="0.3">
@@ -4309,10 +4225,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="C47" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="D47" t="s">
         <v>23</v>
@@ -4324,40 +4240,37 @@
         <v>24</v>
       </c>
       <c r="L47" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="M47" t="s">
         <v>25</v>
       </c>
       <c r="N47" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="O47" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="P47" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="Q47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R47" t="b">
-        <v>1</v>
-      </c>
-      <c r="S47" t="s">
-        <v>414</v>
+        <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>415</v>
+        <v>385</v>
       </c>
       <c r="U47" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V47" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W47" t="s">
-        <v>416</v>
+        <v>386</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.3">
@@ -4365,10 +4278,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>417</v>
+        <v>387</v>
       </c>
       <c r="C48" t="s">
-        <v>418</v>
+        <v>388</v>
       </c>
       <c r="D48" t="s">
         <v>23</v>
@@ -4380,40 +4293,37 @@
         <v>24</v>
       </c>
       <c r="L48" t="s">
-        <v>419</v>
+        <v>389</v>
       </c>
       <c r="M48" t="s">
         <v>25</v>
       </c>
       <c r="N48" t="s">
-        <v>420</v>
+        <v>390</v>
       </c>
       <c r="O48" t="s">
-        <v>421</v>
+        <v>391</v>
       </c>
       <c r="P48" t="s">
-        <v>422</v>
+        <v>392</v>
       </c>
       <c r="Q48" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R48" t="b">
-        <v>1</v>
-      </c>
-      <c r="S48" t="s">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>424</v>
+        <v>393</v>
       </c>
       <c r="U48" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V48" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W48" t="s">
-        <v>425</v>
+        <v>394</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.3">
@@ -4421,10 +4331,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>426</v>
+        <v>395</v>
       </c>
       <c r="C49" t="s">
-        <v>427</v>
+        <v>396</v>
       </c>
       <c r="D49" t="s">
         <v>23</v>
@@ -4436,40 +4346,93 @@
         <v>24</v>
       </c>
       <c r="L49" t="s">
-        <v>428</v>
+        <v>397</v>
       </c>
       <c r="M49" t="s">
         <v>25</v>
       </c>
       <c r="N49" t="s">
-        <v>429</v>
+        <v>398</v>
       </c>
       <c r="O49" t="s">
-        <v>430</v>
+        <v>399</v>
       </c>
       <c r="P49" t="s">
-        <v>431</v>
+        <v>400</v>
       </c>
       <c r="Q49" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R49" t="b">
         <v>1</v>
       </c>
       <c r="S49" t="s">
-        <v>43</v>
+        <v>410</v>
       </c>
       <c r="T49" t="s">
-        <v>48</v>
+        <v>401</v>
       </c>
       <c r="U49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V49" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W49" t="s">
-        <v>432</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>403</v>
+      </c>
+      <c r="C50" t="s">
+        <v>404</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="J50" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" t="s">
+        <v>405</v>
+      </c>
+      <c r="M50" t="s">
+        <v>25</v>
+      </c>
+      <c r="N50" t="s">
+        <v>406</v>
+      </c>
+      <c r="O50" t="s">
+        <v>407</v>
+      </c>
+      <c r="P50" t="s">
+        <v>408</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>28</v>
+      </c>
+      <c r="R50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="s">
+        <v>41</v>
+      </c>
+      <c r="U50" t="s">
+        <v>29</v>
+      </c>
+      <c r="V50" t="s">
+        <v>27</v>
+      </c>
+      <c r="W50" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
